--- a/data/trans_orig/IP16A12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>23768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31467</t>
+          <t>31403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41948</t>
+          <t>42017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>66179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80742</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,18%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13463</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>42557</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62741</t>
+          <t>62795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75060</t>
+          <t>74614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>25913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67218</t>
+          <t>67384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78039</t>
+          <t>78391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>47449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>58676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118774</t>
+          <t>118472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136254</t>
+          <t>135852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>46478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144008</t>
+          <t>143728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164667</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135576</t>
+          <t>136231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154360</t>
+          <t>155238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286297</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315623</t>
+          <t>316939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A12_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5397</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7905</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3698</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6524</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12036</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9528</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14197</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>54,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>81,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12693</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9867</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14680</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>77,44%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>19486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31403</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,63%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21357</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>26286</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>34959</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36475</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30987</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40711</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>28212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42017</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>74250</t>
+          <t>63720</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66179</t>
+          <t>56658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>68720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7255</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6595</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10949</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36716</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31677</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30556</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26202</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33654</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82,25%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>69273</t>
+          <t>67865</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62795</t>
+          <t>60988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74614</t>
+          <t>73480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10948</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16978</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5228</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11802</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>24192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51892</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45862</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56940</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>73958</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>67384</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78391</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>45869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58676</t>
+          <t>48991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>128010</t>
+          <t>97761</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118472</t>
+          <t>89968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135852</t>
+          <t>103633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62840</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62840</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62840</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>79186</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>79186</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>79186</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>144385</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144385</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144385</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33552</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25608</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42931</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25669</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15258</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35624</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131927</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122548</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139871</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>143728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>164094</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>145974</t>
+          <t>120684</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136231</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155238</t>
+          <t>127195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>299657</t>
+          <t>252610</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>240630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316939</t>
+          <t>262864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
